--- a/data.xlsx
+++ b/data.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\桌面文件\search\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\桌面文件\index\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0731295B-2302-4B38-B4F1-53D5E6845131}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE1F9798-0102-4BC2-9913-74F108FC33AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="62">
   <si>
     <t>s</t>
   </si>
@@ -63,39 +63,6 @@
     <t>测试内容10</t>
   </si>
   <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>示例数据1</t>
-  </si>
-  <si>
-    <t>示例数据2</t>
-  </si>
-  <si>
-    <t>示例数据3</t>
-  </si>
-  <si>
-    <t>示例数据4</t>
-  </si>
-  <si>
-    <t>示例数据5</t>
-  </si>
-  <si>
-    <t>示例数据6</t>
-  </si>
-  <si>
-    <t>示例数据7</t>
-  </si>
-  <si>
-    <t>示例数据8</t>
-  </si>
-  <si>
-    <t>示例数据9</t>
-  </si>
-  <si>
-    <t>示例数据10</t>
-  </si>
-  <si>
     <t>名称</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -253,6 +220,46 @@
   </si>
   <si>
     <t>自 2023年09月20日 至 2028年09月20日</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>江苏省脑科医院</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>12320000MB1W2699XR</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>C11627F67AAABBB2FE1479D35B18E0EF</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>开展精神障碍等疾病的预防、治疗、康复、健康管理和教学科研等工作，为全省精神卫生机构提供业务技术指导。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>南京市江宁区淳化街道吴墅社区淳谷路1号</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>杜晨阳</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>江苏省卫生健康委员会</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10万元</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>差额拨款</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>自 2023年08月30日 至 2028年08月30日</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -291,7 +298,7 @@
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -301,6 +308,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFC000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -332,7 +345,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -341,6 +354,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -626,7 +642,9 @@
   <dimension ref="A1:K6"/>
   <sheetFormatPr defaultColWidth="18.9296875" defaultRowHeight="21" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="16384" width="18.9296875" style="1"/>
+    <col min="1" max="9" width="18.9296875" style="1"/>
+    <col min="10" max="10" width="18.9296875" style="4"/>
+    <col min="11" max="16384" width="18.9296875" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" s="2" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.4">
@@ -634,34 +652,34 @@
         <v>0</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="J1" s="3" t="s">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="K1" s="3" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
     </row>
     <row r="2" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.4">
@@ -692,7 +710,7 @@
       <c r="I2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="J2" s="1" t="s">
+      <c r="J2" s="4" t="s">
         <v>10</v>
       </c>
       <c r="K2" s="1" t="s">
@@ -701,42 +719,42 @@
     </row>
     <row r="3" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="1" t="s">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="J3" s="1" t="s">
-        <v>21</v>
+        <v>29</v>
+      </c>
+      <c r="J3" s="4" t="s">
+        <v>30</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>22</v>
+        <v>31</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>33</v>
@@ -745,98 +763,98 @@
         <v>34</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="J4" s="1" t="s">
         <v>41</v>
       </c>
+      <c r="J4" s="4" t="s">
+        <v>42</v>
+      </c>
       <c r="K4" s="1" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
     </row>
     <row r="5" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D5" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="B5" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="D5" s="1" t="s">
+      <c r="E5" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="E5" s="1" t="s">
+      <c r="F5" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="F5" s="1" t="s">
+      <c r="G5" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="H5" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="G5" s="1" t="s">
+      <c r="I5" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="H5" s="1" t="s">
+      <c r="J5" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="I5" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="J5" s="1" t="s">
-        <v>53</v>
-      </c>
       <c r="K5" s="1" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
     </row>
     <row r="6" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="E6" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="B6" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="D6" s="1" t="s">
+      <c r="F6" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="E6" s="1" t="s">
+      <c r="G6" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="I6" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="F6" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="G6" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="H6" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="I6" s="1" t="s">
+      <c r="J6" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="J6" s="1" t="s">
-        <v>62</v>
-      </c>
       <c r="K6" s="1" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
     </row>
   </sheetData>

--- a/data.xlsx
+++ b/data.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\桌面文件\index\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\桌面文件\sydwCx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE1F9798-0102-4BC2-9913-74F108FC33AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{542C7B01-49FB-4274-B67C-4972D02D4B7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="82">
   <si>
     <t>s</t>
   </si>
@@ -57,9 +57,6 @@
     <t>测试内容8</t>
   </si>
   <si>
-    <t>测试内容9</t>
-  </si>
-  <si>
     <t>测试内容10</t>
   </si>
   <si>
@@ -260,6 +257,90 @@
   </si>
   <si>
     <t>自 2023年08月30日 至 2028年08月30日</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>济南市长清区人民医院</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>123701134931404810</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>齐良民</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>济南市长清区卫生健康局</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>财政补贴</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>91929.93万元</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>济南市长清区大学路5000号</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>向社会提供医疗预防、保健、康复、急救、医学咨询及社区服务，进行医学研究，承担高、中级卫生专业人才培养。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>自 2000年00月00日 至 2000年00月00日</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>自 2024年11月13日 至 2026年03月31日</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>8511EB88C0F1B7852F3C3DE3AF36BE61</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>胜利油田中心医院（东营市职业病防治院）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>12370500706161391X</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>7CDDE6F96518FDAEB1F8B44B4441162B</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>山东省东营市济南路31号</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>面向社会提供医疗、预防、保健、康复等服务，承担相关研究、教学、科研及药物制剂、公共卫生服务、职业病诊疗等任务。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>颜培光</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>经费自理</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>122146.63万元</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>东营市卫生健康委员会</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>自 2026年02月25日 至 2031年03月31日</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -298,7 +379,7 @@
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -314,6 +395,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF92D050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B0F0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -345,7 +432,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -357,6 +444,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -639,7 +729,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K6"/>
+  <dimension ref="A1:K8"/>
   <sheetFormatPr defaultColWidth="18.9296875" defaultRowHeight="21" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="9" width="18.9296875" style="1"/>
@@ -652,34 +742,34 @@
         <v>0</v>
       </c>
       <c r="B1" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="D1" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="E1" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="F1" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="G1" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="H1" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="I1" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="J1" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="K1" s="3" t="s">
         <v>20</v>
-      </c>
-      <c r="K1" s="3" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="2" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.4">
@@ -710,151 +800,221 @@
       <c r="I2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="J2" s="4" t="s">
+      <c r="J2" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="K2" s="1" t="s">
         <v>10</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="3" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="D3" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="E3" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="F3" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="G3" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="H3" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="H3" s="1" t="s">
+      <c r="I3" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="I3" s="1" t="s">
+      <c r="J3" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="J3" s="4" t="s">
+      <c r="K3" s="1" t="s">
         <v>30</v>
-      </c>
-      <c r="K3" s="1" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D4" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="B4" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="D4" s="1" t="s">
+      <c r="E4" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="F4" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="G4" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="G4" s="1" t="s">
+      <c r="H4" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="H4" s="1" t="s">
+      <c r="I4" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="I4" s="1" t="s">
+      <c r="J4" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="J4" s="4" t="s">
-        <v>42</v>
-      </c>
       <c r="K4" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="5" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D5" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="B5" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="D5" s="1" t="s">
+      <c r="E5" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="E5" s="1" t="s">
+      <c r="F5" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="F5" s="1" t="s">
+      <c r="G5" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="H5" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="G5" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="H5" s="1" t="s">
+      <c r="I5" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="I5" s="1" t="s">
+      <c r="J5" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="J5" s="4" t="s">
-        <v>51</v>
-      </c>
       <c r="K5" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="6" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="D6" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="B6" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="D6" s="1" t="s">
+      <c r="E6" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="E6" s="1" t="s">
+      <c r="F6" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="F6" s="1" t="s">
+      <c r="G6" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="I6" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="G6" s="1" t="s">
+      <c r="J6" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="H6" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="I6" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="J6" s="4" t="s">
+      <c r="K6" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A7" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="B7" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="K6" s="1" t="s">
-        <v>31</v>
+      <c r="C7" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="J7" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="K7" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A8" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="I8" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="J8" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="K8" s="1" t="s">
+        <v>30</v>
       </c>
     </row>
   </sheetData>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\桌面文件\sydwCx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{542C7B01-49FB-4274-B67C-4972D02D4B7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1CF20D4-77E7-4785-A2BC-DB9D6EAE9488}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="102">
   <si>
     <t>s</t>
   </si>
@@ -341,6 +341,86 @@
   </si>
   <si>
     <t>自 2026年02月25日 至 2031年03月31日</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>四川省数字体育发展中心</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>12510000744674518P</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>312F952D4202CEBC470CEBABB717B33B</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>吴国栋</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>5万元</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>四川省体育局</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>财政补助（核定收支、定额补助）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>四川省成都市青羊区大石西路6号</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>负责全省体育数字化事务性工作；组织开展体育网络技术业务培训；负责省体育局系统信息化建设和运维管理；参与体育信息化发展政策和规划研究。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>雅安市体育发展中心</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>125116000541350311</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>林涛</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>20万元</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>财政补助（全额拨款）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>雅安市文化广播电视体育和旅游局</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>雨城区沙湾金凤路7号</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>多措并举促进全民健身，负责组织、指导、协调本区域群众性体育活动，并做好体育法律、法规宣传工作；开展体育健身咨询活动，保障群众参加体育锻炼的合法权益，指导、协调本区域各单位和各部门开展全民健身活动；指导、协调本区域体协等体育群众团体开展群众体育活动；为国家培养输送体育后备人才；负责体育场馆运营管理及产业发展。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>9D2BDE6BE44A2EDA67D5F43A40E24ACE</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>自 2024年05月06日 至 2029年05月05日</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>自 2025年03月18日 至 2030年03月17日</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -729,10 +809,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K8"/>
+  <dimension ref="A1:K10"/>
   <sheetFormatPr defaultColWidth="18.9296875" defaultRowHeight="21" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="9" width="18.9296875" style="1"/>
+    <col min="1" max="1" width="18.9296875" style="1"/>
+    <col min="2" max="2" width="27.3984375" style="1" customWidth="1"/>
+    <col min="3" max="9" width="18.9296875" style="1"/>
     <col min="10" max="10" width="18.9296875" style="4"/>
     <col min="11" max="16384" width="18.9296875" style="1"/>
   </cols>
@@ -1017,6 +1099,76 @@
         <v>30</v>
       </c>
     </row>
+    <row r="9" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A9" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="I9" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="J9" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="K9" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A10" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="H10" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="I10" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="J10" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="K10" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data.xlsx
+++ b/data.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\桌面文件\sydwCx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1CF20D4-77E7-4785-A2BC-DB9D6EAE9488}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07CC1F50-27F7-49F1-AB0F-F727AF0054D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="121">
   <si>
     <t>s</t>
   </si>
@@ -421,6 +421,82 @@
   </si>
   <si>
     <t>自 2025年03月18日 至 2030年03月17日</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>晋中市体育馆</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>121408006744833369</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>42.48万元</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>赵园明</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>晋中市榆次区安宁东街体育公园内</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>提供训练比赛基地，培训体育骨干 为广大人民群众提供良好的健身场所。 举办大型体育赛事及其它大型活动 为全民健身服务</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>晋中市体育局</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>自 2022年03月09日 至 2027年03月09日</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>16D2E60533A32C54DFCFCD677C197C2B</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>阳泉市体育产业发展中心</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>12140300MB169311X6</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>A65360433A2D87BF49C097293D1F5DB4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>张超</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4.8万元</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>阳泉市城区南大街452号</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>推动全市体育产业发展。制定全市体育产业发展规划 推进全市体育产业发展 监测分析全市体育产业运行态势 协调解决体育产业发展过程中的重大问题 规范和培育体育产业市场 监督、检查和管理全市体育经营活动 协助开展城、矿区体育市场执法检查工作 保护合法经营 制止和查处违法行为 开展对体育产业从业人员的培训 参与体育产业经营场所标准的验收评估</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>财政补助（财政拨款）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>阳泉市体育局</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>自 2023年06月06日 至 2028年06月05日</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -459,7 +535,7 @@
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -481,6 +557,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF00B0F0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -517,9 +599,6 @@
     <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="49" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -527,6 +606,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="3" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -809,48 +891,54 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K10"/>
+  <dimension ref="A1:K12"/>
   <sheetFormatPr defaultColWidth="18.9296875" defaultRowHeight="21" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="18.9296875" style="1"/>
-    <col min="2" max="2" width="27.3984375" style="1" customWidth="1"/>
-    <col min="3" max="9" width="18.9296875" style="1"/>
-    <col min="10" max="10" width="18.9296875" style="4"/>
+    <col min="2" max="2" width="27.3984375" style="5" customWidth="1"/>
+    <col min="3" max="3" width="18.9296875" style="5"/>
+    <col min="4" max="4" width="21" style="5" customWidth="1"/>
+    <col min="5" max="5" width="30.59765625" style="5" customWidth="1"/>
+    <col min="6" max="6" width="12.59765625" style="5" customWidth="1"/>
+    <col min="7" max="7" width="14" style="5" customWidth="1"/>
+    <col min="8" max="8" width="14.265625" style="5" customWidth="1"/>
+    <col min="9" max="9" width="18.9296875" style="5"/>
+    <col min="10" max="10" width="18.9296875" style="3"/>
     <col min="11" max="16384" width="18.9296875" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" s="2" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="I1" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="J1" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="K1" s="2" t="s">
         <v>20</v>
       </c>
     </row>
@@ -858,31 +946,31 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="D2" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="E2" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="F2" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="G2" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="H2" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="I2" s="1" t="s">
+      <c r="I2" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="J2" s="5" t="s">
+      <c r="J2" s="4" t="s">
         <v>69</v>
       </c>
       <c r="K2" s="1" t="s">
@@ -893,31 +981,31 @@
       <c r="A3" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C3" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="D3" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="E3" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="F3" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="G3" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="H3" s="1" t="s">
+      <c r="H3" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="I3" s="1" t="s">
+      <c r="I3" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="J3" s="4" t="s">
+      <c r="J3" s="3" t="s">
         <v>29</v>
       </c>
       <c r="K3" s="1" t="s">
@@ -928,31 +1016,31 @@
       <c r="A4" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="B4" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="C4" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="D4" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="E4" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="F4" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="G4" s="1" t="s">
+      <c r="G4" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="H4" s="1" t="s">
+      <c r="H4" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="I4" s="1" t="s">
+      <c r="I4" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="J4" s="4" t="s">
+      <c r="J4" s="3" t="s">
         <v>41</v>
       </c>
       <c r="K4" s="1" t="s">
@@ -963,31 +1051,31 @@
       <c r="A5" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="B5" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="C5" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="D5" s="1" t="s">
+      <c r="D5" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="E5" s="1" t="s">
+      <c r="E5" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="F5" s="1" t="s">
+      <c r="F5" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="G5" s="1" t="s">
+      <c r="G5" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="H5" s="1" t="s">
+      <c r="H5" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="I5" s="1" t="s">
+      <c r="I5" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="J5" s="4" t="s">
+      <c r="J5" s="3" t="s">
         <v>50</v>
       </c>
       <c r="K5" s="1" t="s">
@@ -998,31 +1086,31 @@
       <c r="A6" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="B6" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="C6" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="D6" s="1" t="s">
+      <c r="D6" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="E6" s="1" t="s">
+      <c r="E6" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="F6" s="1" t="s">
+      <c r="F6" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="G6" s="1" t="s">
+      <c r="G6" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="H6" s="1" t="s">
+      <c r="H6" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="I6" s="1" t="s">
+      <c r="I6" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="J6" s="4" t="s">
+      <c r="J6" s="3" t="s">
         <v>60</v>
       </c>
       <c r="K6" s="1" t="s">
@@ -1033,31 +1121,31 @@
       <c r="A7" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="B7" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="C7" s="1" t="s">
+      <c r="C7" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="D7" s="1" t="s">
+      <c r="D7" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="E7" s="1" t="s">
+      <c r="E7" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="F7" s="1" t="s">
+      <c r="F7" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="G7" s="1" t="s">
+      <c r="G7" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="H7" s="1" t="s">
+      <c r="H7" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="I7" s="1" t="s">
+      <c r="I7" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="J7" s="4" t="s">
+      <c r="J7" s="3" t="s">
         <v>70</v>
       </c>
       <c r="K7" s="1" t="s">
@@ -1068,31 +1156,31 @@
       <c r="A8" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="B8" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="C8" s="1" t="s">
+      <c r="C8" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="D8" s="1" t="s">
+      <c r="D8" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="E8" s="1" t="s">
+      <c r="E8" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="F8" s="1" t="s">
+      <c r="F8" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="G8" s="1" t="s">
+      <c r="G8" s="5" t="s">
         <v>78</v>
       </c>
-      <c r="H8" s="1" t="s">
+      <c r="H8" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="I8" s="1" t="s">
+      <c r="I8" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="J8" s="4" t="s">
+      <c r="J8" s="3" t="s">
         <v>81</v>
       </c>
       <c r="K8" s="1" t="s">
@@ -1103,31 +1191,31 @@
       <c r="A9" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="B9" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="C9" s="1" t="s">
+      <c r="C9" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="D9" s="1" t="s">
+      <c r="D9" s="5" t="s">
         <v>90</v>
       </c>
-      <c r="E9" s="1" t="s">
+      <c r="E9" s="5" t="s">
         <v>89</v>
       </c>
-      <c r="F9" s="1" t="s">
+      <c r="F9" s="5" t="s">
         <v>85</v>
       </c>
-      <c r="G9" s="1" t="s">
+      <c r="G9" s="5" t="s">
         <v>88</v>
       </c>
-      <c r="H9" s="1" t="s">
+      <c r="H9" s="5" t="s">
         <v>86</v>
       </c>
-      <c r="I9" s="1" t="s">
+      <c r="I9" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="J9" s="5" t="s">
+      <c r="J9" s="4" t="s">
         <v>101</v>
       </c>
       <c r="K9" s="1" t="s">
@@ -1138,34 +1226,104 @@
       <c r="A10" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="B10" s="1" t="s">
+      <c r="B10" s="5" t="s">
         <v>91</v>
       </c>
-      <c r="C10" s="1" t="s">
+      <c r="C10" s="5" t="s">
         <v>92</v>
       </c>
-      <c r="D10" s="1" t="s">
+      <c r="D10" s="5" t="s">
         <v>98</v>
       </c>
-      <c r="E10" s="1" t="s">
+      <c r="E10" s="5" t="s">
         <v>97</v>
       </c>
-      <c r="F10" s="1" t="s">
+      <c r="F10" s="5" t="s">
         <v>93</v>
       </c>
-      <c r="G10" s="1" t="s">
+      <c r="G10" s="5" t="s">
         <v>95</v>
       </c>
-      <c r="H10" s="1" t="s">
+      <c r="H10" s="5" t="s">
         <v>94</v>
       </c>
-      <c r="I10" s="1" t="s">
+      <c r="I10" s="5" t="s">
         <v>96</v>
       </c>
-      <c r="J10" s="5" t="s">
+      <c r="J10" s="4" t="s">
         <v>100</v>
       </c>
       <c r="K10" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A11" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="G11" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="H11" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="I11" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="J11" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="K11" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A12" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="E12" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="F12" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="G12" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="H12" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="I12" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="J12" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="K12" s="1" t="s">
         <v>30</v>
       </c>
     </row>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\桌面文件\sydwCx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07CC1F50-27F7-49F1-AB0F-F727AF0054D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03D6533F-292F-4C08-9FAB-2DA805F1765D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="131">
   <si>
     <t>s</t>
   </si>
@@ -497,6 +497,46 @@
   </si>
   <si>
     <t>自 2023年06月06日 至 2028年06月05日</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>桂林市第二体育馆</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>12450300G389000867</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>赵珊珊</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>57.3万元</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>桂林市三皇路8号</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>提供训练，比赛与相关服务，促进体育事业发展；承办各种比赛、演出、展销会，训练场地提供与管理（相关社会服务）。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>财政补助</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>桂林市体育局</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>自 2025年07月11日 至 2030年07月10日</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>D2B436DF07AD24EC912CBBC4D5C00511</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -891,7 +931,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K12"/>
+  <dimension ref="A1:K13"/>
   <sheetFormatPr defaultColWidth="18.9296875" defaultRowHeight="21" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="18.9296875" style="1"/>
@@ -1327,6 +1367,41 @@
         <v>30</v>
       </c>
     </row>
+    <row r="13" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A13" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>121</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="E13" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="F13" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="G13" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="H13" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="I13" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="J13" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="K13" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\桌面文件\sydwCx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03D6533F-292F-4C08-9FAB-2DA805F1765D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CFFD3C8A-C9EA-4893-9D95-6C45D4380E7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="140">
   <si>
     <t>s</t>
   </si>
@@ -537,6 +537,42 @@
   </si>
   <si>
     <t>D2B436DF07AD24EC912CBBC4D5C00511</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>邹平市人民医院</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>段涛</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>123716264947202265</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>A6A0DB0A39FFB552FD748A8C499D4A11</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>邹平市鹤伴二路823号</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>为人民身体健康提供医疗与护理保健服务。医疗与护理；养老服务、培训；医学教学；医学研究；卫生医疗人员培训；卫生技术人员继续教育；保健与健康教育。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1256.1万元</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>邹平市卫生健康局</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>自 2026年01月27日 至 2030年03月31日</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -931,7 +967,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K13"/>
+  <dimension ref="A1:K14"/>
   <sheetFormatPr defaultColWidth="18.9296875" defaultRowHeight="21" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="18.9296875" style="1"/>
@@ -1402,6 +1438,41 @@
         <v>30</v>
       </c>
     </row>
+    <row r="14" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A14" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>131</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="E14" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="F14" s="5" t="s">
+        <v>132</v>
+      </c>
+      <c r="G14" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="H14" s="5" t="s">
+        <v>137</v>
+      </c>
+      <c r="I14" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="J14" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="K14" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\桌面文件\sydwCx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CFFD3C8A-C9EA-4893-9D95-6C45D4380E7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E283951-F549-42EE-852E-A8A1DDE34EF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="140">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="149">
   <si>
     <t>s</t>
   </si>
@@ -573,6 +573,42 @@
   </si>
   <si>
     <t>自 2026年01月27日 至 2030年03月31日</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>凌源市电视转播台</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>12211382465010030J</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>84F2CA6ACE9B7BAF5BDBE35DEB76B405</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>王立秋</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>36万元</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>凌源市文旅体育和广播电视技术保障中心</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>自 2023年12月06日 至 2028年12月05日</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>负责本行政辖区内广播电视信号无线传输覆盖，负责中央、省、市、县四级相关频率频道的广播电视传输、发射有关技术保障工作；对全市广播电视的传输发射运行情况进行监测；负责全市农村无线数字广播电视信号的覆盖规划的编制、运营维护和管理工作提供技术支持和服务保障。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>凌源市铁西二街20号</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -967,7 +1003,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K14"/>
+  <dimension ref="A1:K16"/>
   <sheetFormatPr defaultColWidth="18.9296875" defaultRowHeight="21" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="18.9296875" style="1"/>
@@ -1291,7 +1327,7 @@
       <c r="I9" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="J9" s="4" t="s">
+      <c r="J9" s="3" t="s">
         <v>101</v>
       </c>
       <c r="K9" s="1" t="s">
@@ -1326,7 +1362,7 @@
       <c r="I10" s="5" t="s">
         <v>96</v>
       </c>
-      <c r="J10" s="4" t="s">
+      <c r="J10" s="3" t="s">
         <v>100</v>
       </c>
       <c r="K10" s="1" t="s">
@@ -1361,7 +1397,7 @@
       <c r="I11" s="5" t="s">
         <v>108</v>
       </c>
-      <c r="J11" s="4" t="s">
+      <c r="J11" s="3" t="s">
         <v>109</v>
       </c>
       <c r="K11" s="1" t="s">
@@ -1396,7 +1432,7 @@
       <c r="I12" s="5" t="s">
         <v>119</v>
       </c>
-      <c r="J12" s="4" t="s">
+      <c r="J12" s="3" t="s">
         <v>120</v>
       </c>
       <c r="K12" s="1" t="s">
@@ -1431,7 +1467,7 @@
       <c r="I13" s="5" t="s">
         <v>128</v>
       </c>
-      <c r="J13" s="4" t="s">
+      <c r="J13" s="3" t="s">
         <v>129</v>
       </c>
       <c r="K13" s="1" t="s">
@@ -1466,12 +1502,50 @@
       <c r="I14" s="5" t="s">
         <v>138</v>
       </c>
-      <c r="J14" s="4" t="s">
+      <c r="J14" s="3" t="s">
         <v>139</v>
       </c>
       <c r="K14" s="1" t="s">
         <v>30</v>
       </c>
+    </row>
+    <row r="15" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A15" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>141</v>
+      </c>
+      <c r="D15" s="5" t="s">
+        <v>147</v>
+      </c>
+      <c r="E15" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="F15" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="G15" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="H15" s="5" t="s">
+        <v>144</v>
+      </c>
+      <c r="I15" s="5" t="s">
+        <v>145</v>
+      </c>
+      <c r="J15" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="K15" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="J16" s="4"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\桌面文件\sydwCx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E283951-F549-42EE-852E-A8A1DDE34EF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A665A32-ED38-4D18-8F77-BCBDE5F5D37E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="149">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="166">
   <si>
     <t>s</t>
   </si>
@@ -609,6 +609,74 @@
   </si>
   <si>
     <t>凌源市铁西二街20号</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>山西省冰雪运动中心</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>12140000MB1E386443</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>32BFCB90CFE33D137B341CE68B6AC317</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>黄海宏</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>山西省体育局</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>山西省太原市晋源区健康南街1号</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>协助拟订冰雪体育运动项目的发展规划，负责全省冰雪体育运动项目的业务指导和管理，推动冰雪体育运动项目的普及 负责冰雪体育运动项目运动队的建设以及后备人才培养 指导社会群团和组织推动冰雪体育运动项目的群众性活动和全民健身运动的开展</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>自 2026年03月04日 至 2028年03月03日</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>天津市小球运动管理中心</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>12120000MB1D178854</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>李晶</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>150万元</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>天津市体育局</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>天津市静海区健康产业园区团泊体育中心</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>本单位的宗旨是为中国奥运争光计划服务，为天津竞技体育发展添彩。本单位的业务范围包括：（一）承担本市竞技体育球类项目（不含足球、篮球、排球、网球及非全运会球类项目）业务管理；（二）承担专业运动队管理和体育后备人才培养；（三）承办国家体育总局和本市竞技体育球类项目的竞赛。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>C0DE754A658C88DA119CB01C28D0A1AF</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>自 2025年03月31日 至 2030年03月30日</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1003,7 +1071,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K16"/>
+  <dimension ref="A1:K17"/>
   <sheetFormatPr defaultColWidth="18.9296875" defaultRowHeight="21" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="18.9296875" style="1"/>
@@ -1545,7 +1613,74 @@
       </c>
     </row>
     <row r="16" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="J16" s="4"/>
+      <c r="A16" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="D16" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="E16" s="5" t="s">
+        <v>154</v>
+      </c>
+      <c r="F16" s="5" t="s">
+        <v>152</v>
+      </c>
+      <c r="G16" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="H16" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="I16" s="5" t="s">
+        <v>153</v>
+      </c>
+      <c r="J16" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="K16" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A17" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="C17" s="5" t="s">
+        <v>158</v>
+      </c>
+      <c r="D17" s="5" t="s">
+        <v>163</v>
+      </c>
+      <c r="E17" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="F17" s="5" t="s">
+        <v>159</v>
+      </c>
+      <c r="G17" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="H17" s="5" t="s">
+        <v>160</v>
+      </c>
+      <c r="I17" s="5" t="s">
+        <v>161</v>
+      </c>
+      <c r="J17" s="4" t="s">
+        <v>165</v>
+      </c>
+      <c r="K17" s="1" t="s">
+        <v>30</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\桌面文件\sydwCx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A665A32-ED38-4D18-8F77-BCBDE5F5D37E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7795F10E-0F09-44BE-9087-E5AE8280803E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="166">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="166">
   <si>
     <t>s</t>
   </si>
@@ -1071,7 +1071,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K17"/>
+  <dimension ref="A1:K18"/>
   <sheetFormatPr defaultColWidth="18.9296875" defaultRowHeight="21" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="18.9296875" style="1"/>
@@ -1682,6 +1682,41 @@
         <v>30</v>
       </c>
     </row>
+    <row r="18" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A18" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="C18" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="D18" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="E18" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="F18" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="G18" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="H18" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="I18" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="J18" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="K18" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\桌面文件\sydwCx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7795F10E-0F09-44BE-9087-E5AE8280803E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B85DF31-BB2B-475F-B1BC-06E28821D73F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="166">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="176">
   <si>
     <t>s</t>
   </si>
@@ -677,6 +677,46 @@
   </si>
   <si>
     <t>自 2025年03月31日 至 2030年03月30日</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>常州市金坛区社会福利中心</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>12320482467505491U</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>卞俊</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>11万元</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>常州市金坛区民政局</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>自 2026年05月12日 至 2031年05月12日</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>全额拨款</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>常州市金坛区东环一路669号7号楼1楼</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>负责福利彩票销售和管理，负责社会老人寄养、孤儿收养，负责困难家庭经济状况核对</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>8923E644C453BA4CF7A375BC0BFE05DA</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1071,7 +1111,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K18"/>
+  <dimension ref="A1:K19"/>
   <sheetFormatPr defaultColWidth="18.9296875" defaultRowHeight="21" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="18.9296875" style="1"/>
@@ -1605,7 +1645,7 @@
       <c r="I15" s="5" t="s">
         <v>145</v>
       </c>
-      <c r="J15" s="4" t="s">
+      <c r="J15" s="3" t="s">
         <v>146</v>
       </c>
       <c r="K15" s="1" t="s">
@@ -1640,7 +1680,7 @@
       <c r="I16" s="5" t="s">
         <v>153</v>
       </c>
-      <c r="J16" s="4" t="s">
+      <c r="J16" s="3" t="s">
         <v>156</v>
       </c>
       <c r="K16" s="1" t="s">
@@ -1675,7 +1715,7 @@
       <c r="I17" s="5" t="s">
         <v>161</v>
       </c>
-      <c r="J17" s="4" t="s">
+      <c r="J17" s="3" t="s">
         <v>165</v>
       </c>
       <c r="K17" s="1" t="s">
@@ -1710,10 +1750,45 @@
       <c r="I18" s="5" t="s">
         <v>108</v>
       </c>
-      <c r="J18" s="4" t="s">
+      <c r="J18" s="3" t="s">
         <v>109</v>
       </c>
       <c r="K18" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A19" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>166</v>
+      </c>
+      <c r="C19" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="D19" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="E19" s="5" t="s">
+        <v>173</v>
+      </c>
+      <c r="F19" s="5" t="s">
+        <v>168</v>
+      </c>
+      <c r="G19" s="5" t="s">
+        <v>172</v>
+      </c>
+      <c r="H19" s="5" t="s">
+        <v>169</v>
+      </c>
+      <c r="I19" s="5" t="s">
+        <v>170</v>
+      </c>
+      <c r="J19" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="K19" s="1" t="s">
         <v>30</v>
       </c>
     </row>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\桌面文件\sydwCx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B85DF31-BB2B-475F-B1BC-06E28821D73F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77C8A12F-E14E-4B80-8C31-92415644AB2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="176">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="194">
   <si>
     <t>s</t>
   </si>
@@ -717,6 +717,78 @@
   </si>
   <si>
     <t>8923E644C453BA4CF7A375BC0BFE05DA</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>河北省体育发展交流中心</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>12130000MB1M16805D</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>7695839AFC489F11B426D946AC607B49</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>董克清</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>34.32万元</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>河北省石家庄市长安区体育南大街8号</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>选聘、招聘和调动运动员，申报、发放关怀基金；全省体育行业特有工种职业技能鉴定以及体育系统人员职业技能培训；体育专家人才服务保障；管理省体育局系统人事档案；全省体育系统安全生产监管及高危险性体育项目安全监管；省体育局系统涉外事务服务保障；组织开展与国外及港澳台的体育交流，办理本系统人员出访手续。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>河北省体育局</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>自 2026年05月07日 至 2031年05月06日</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>安庆市广播电视发射中心</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>12340800697357711M</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>34675991D5FAC2585E5A43FB1CE513C6</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>王俊</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>110万元</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>安庆市新闻传媒中心</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>安庆市开发区广播电视中心大楼</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>为市广播电台和电视台节目转播服务。 承担安庆市广播电视发射任务，确保我市广播电台、电视台节目的覆盖。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>自 2021年12月21日 至 2026年12月21日</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1111,7 +1183,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K19"/>
+  <dimension ref="A1:K21"/>
   <sheetFormatPr defaultColWidth="18.9296875" defaultRowHeight="21" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="18.9296875" style="1"/>
@@ -1792,6 +1864,76 @@
         <v>30</v>
       </c>
     </row>
+    <row r="20" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A20" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>176</v>
+      </c>
+      <c r="C20" s="5" t="s">
+        <v>177</v>
+      </c>
+      <c r="D20" s="5" t="s">
+        <v>182</v>
+      </c>
+      <c r="E20" s="5" t="s">
+        <v>181</v>
+      </c>
+      <c r="F20" s="5" t="s">
+        <v>179</v>
+      </c>
+      <c r="G20" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="H20" s="5" t="s">
+        <v>180</v>
+      </c>
+      <c r="I20" s="5" t="s">
+        <v>183</v>
+      </c>
+      <c r="J20" s="4" t="s">
+        <v>184</v>
+      </c>
+      <c r="K20" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A21" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>185</v>
+      </c>
+      <c r="C21" s="5" t="s">
+        <v>186</v>
+      </c>
+      <c r="D21" s="5" t="s">
+        <v>192</v>
+      </c>
+      <c r="E21" s="5" t="s">
+        <v>191</v>
+      </c>
+      <c r="F21" s="5" t="s">
+        <v>188</v>
+      </c>
+      <c r="G21" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="H21" s="5" t="s">
+        <v>189</v>
+      </c>
+      <c r="I21" s="5" t="s">
+        <v>190</v>
+      </c>
+      <c r="J21" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="K21" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\桌面文件\sydwCx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77C8A12F-E14E-4B80-8C31-92415644AB2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{658BB9C0-1435-4A94-990F-78C7A4DDECE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="194">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="242" uniqueCount="202">
   <si>
     <t>s</t>
   </si>
@@ -789,6 +789,38 @@
   </si>
   <si>
     <t>自 2021年12月21日 至 2026年12月21日</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>四川省社会体育指导中心</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>125100007978836395</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>孙勇</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>8万元</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ADBCD286A55568C30658EC8C8EED2568</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>成都市新南路93号亚华商厦5楼</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>指导全省龙舟、滑轮、门球、毽球、风筝、信鸽、健美、健美操、体育舞蹈等社会体育运动项目的开展，推动上述运动项目的普及、提高；负责举办上述运动项目比赛的有关组织工作，开展与上述运动项目有关的多种形式的服务活动；承担省体育局交给的其他社会体育项目的指导、服务工作。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>自 2024年11月01日 至 2029年10月31日</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1183,7 +1215,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K21"/>
+  <dimension ref="A1:K22"/>
   <sheetFormatPr defaultColWidth="18.9296875" defaultRowHeight="21" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="18.9296875" style="1"/>
@@ -1934,6 +1966,41 @@
         <v>30</v>
       </c>
     </row>
+    <row r="22" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A22" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>194</v>
+      </c>
+      <c r="C22" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="D22" s="5" t="s">
+        <v>200</v>
+      </c>
+      <c r="E22" s="5" t="s">
+        <v>199</v>
+      </c>
+      <c r="F22" s="5" t="s">
+        <v>196</v>
+      </c>
+      <c r="G22" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="H22" s="5" t="s">
+        <v>197</v>
+      </c>
+      <c r="I22" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="J22" s="4" t="s">
+        <v>201</v>
+      </c>
+      <c r="K22" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\桌面文件\sydwCx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{658BB9C0-1435-4A94-990F-78C7A4DDECE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DBFFF867-E15F-47BF-8CE6-1BF9B910490F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="242" uniqueCount="202">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="211">
   <si>
     <t>s</t>
   </si>
@@ -821,6 +821,42 @@
   </si>
   <si>
     <t>自 2024年11月01日 至 2029年10月31日</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>吉林省体育职业技能鉴定站</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>12220000673327884F</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>7F434BA3E584FB94A7E2211D0FD83559</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>张丽颖</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>92万元</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>吉林省体育局</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>吉林省长春市南关区吉顺街1202号</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>开展体育职业技能鉴定，为体育事业服务。 组织实施全省体育行业特有工种职业技能鉴定方面的工作</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>自 2023年04月07日 至 2028年04月07日</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1215,7 +1251,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K22"/>
+  <dimension ref="A1:K23"/>
   <sheetFormatPr defaultColWidth="18.9296875" defaultRowHeight="21" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="18.9296875" style="1"/>
@@ -2001,6 +2037,41 @@
         <v>30</v>
       </c>
     </row>
+    <row r="23" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A23" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>202</v>
+      </c>
+      <c r="C23" s="5" t="s">
+        <v>203</v>
+      </c>
+      <c r="D23" s="5" t="s">
+        <v>209</v>
+      </c>
+      <c r="E23" s="5" t="s">
+        <v>208</v>
+      </c>
+      <c r="F23" s="5" t="s">
+        <v>205</v>
+      </c>
+      <c r="G23" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="H23" s="5" t="s">
+        <v>206</v>
+      </c>
+      <c r="I23" s="5" t="s">
+        <v>207</v>
+      </c>
+      <c r="J23" s="4" t="s">
+        <v>210</v>
+      </c>
+      <c r="K23" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\桌面文件\sydwCx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DBFFF867-E15F-47BF-8CE6-1BF9B910490F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8ECE530B-5F60-48BF-8B5E-968C2B175B6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="211">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="221">
   <si>
     <t>s</t>
   </si>
@@ -857,6 +857,46 @@
   </si>
   <si>
     <t>自 2023年04月07日 至 2028年04月07日</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>池州市福利彩票发行中心</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>12341800F16199738H</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>A78577845D3969C7FB3799AC5605B651</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>严建丽</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1万元</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>贵池区罗城路汇景中门16幢门面</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>管理全市福利彩票发行，促进社会福利事业发展。福彩电脑票发行管理、福彩刮刮乐即开票发行管理</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>非财政补助（经费自理）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>池州市民政局</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>自 2023年08月15日 至 2028年08月14日</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1251,7 +1291,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K23"/>
+  <dimension ref="A1:K24"/>
   <sheetFormatPr defaultColWidth="18.9296875" defaultRowHeight="21" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="18.9296875" style="1"/>
@@ -1925,7 +1965,7 @@
       <c r="I19" s="5" t="s">
         <v>170</v>
       </c>
-      <c r="J19" s="4" t="s">
+      <c r="J19" s="3" t="s">
         <v>171</v>
       </c>
       <c r="K19" s="1" t="s">
@@ -1960,7 +2000,7 @@
       <c r="I20" s="5" t="s">
         <v>183</v>
       </c>
-      <c r="J20" s="4" t="s">
+      <c r="J20" s="3" t="s">
         <v>184</v>
       </c>
       <c r="K20" s="1" t="s">
@@ -1995,7 +2035,7 @@
       <c r="I21" s="5" t="s">
         <v>190</v>
       </c>
-      <c r="J21" s="4" t="s">
+      <c r="J21" s="3" t="s">
         <v>193</v>
       </c>
       <c r="K21" s="1" t="s">
@@ -2030,7 +2070,7 @@
       <c r="I22" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="J22" s="4" t="s">
+      <c r="J22" s="3" t="s">
         <v>201</v>
       </c>
       <c r="K22" s="1" t="s">
@@ -2065,10 +2105,45 @@
       <c r="I23" s="5" t="s">
         <v>207</v>
       </c>
-      <c r="J23" s="4" t="s">
+      <c r="J23" s="3" t="s">
         <v>210</v>
       </c>
       <c r="K23" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A24" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>211</v>
+      </c>
+      <c r="C24" s="5" t="s">
+        <v>212</v>
+      </c>
+      <c r="D24" s="5" t="s">
+        <v>217</v>
+      </c>
+      <c r="E24" s="5" t="s">
+        <v>216</v>
+      </c>
+      <c r="F24" s="5" t="s">
+        <v>214</v>
+      </c>
+      <c r="G24" s="5" t="s">
+        <v>218</v>
+      </c>
+      <c r="H24" s="5" t="s">
+        <v>215</v>
+      </c>
+      <c r="I24" s="5" t="s">
+        <v>219</v>
+      </c>
+      <c r="J24" s="4" t="s">
+        <v>220</v>
+      </c>
+      <c r="K24" s="1" t="s">
         <v>30</v>
       </c>
     </row>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\桌面文件\sydwCx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8ECE530B-5F60-48BF-8B5E-968C2B175B6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D489E72-15B6-45C4-BB6F-78DE8D940547}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="221">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="275" uniqueCount="230">
   <si>
     <t>s</t>
   </si>
@@ -897,6 +897,42 @@
   </si>
   <si>
     <t>自 2023年08月15日 至 2028年08月14日</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>西安市阎良区体育场</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>12610114688980720Q</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>刘幼红</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>152.84万元</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>西安市阎良区文化和旅游体育局</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>西安市阎良区蓝天六路中段阎良区文体中心</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>指导全区各项体育运动，促进体育事业发展。优秀运动队建设、后备人才的培养；项目注册管理；竞赛计划规程制定；裁判队伍管理；群众各项体育项目竞赛的管理与组织；教练员、裁判员等级培训。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>11D8D3305D9D70A7D43D5FC7D974BC72</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>自 2026年02月09日 至 2031年02月09日</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1291,7 +1327,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K24"/>
+  <dimension ref="A1:K25"/>
   <sheetFormatPr defaultColWidth="18.9296875" defaultRowHeight="21" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="18.9296875" style="1"/>
@@ -2147,6 +2183,41 @@
         <v>30</v>
       </c>
     </row>
+    <row r="25" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A25" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>221</v>
+      </c>
+      <c r="C25" s="5" t="s">
+        <v>222</v>
+      </c>
+      <c r="D25" s="5" t="s">
+        <v>227</v>
+      </c>
+      <c r="E25" s="5" t="s">
+        <v>226</v>
+      </c>
+      <c r="F25" s="5" t="s">
+        <v>223</v>
+      </c>
+      <c r="G25" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="H25" s="5" t="s">
+        <v>224</v>
+      </c>
+      <c r="I25" s="5" t="s">
+        <v>225</v>
+      </c>
+      <c r="J25" s="4" t="s">
+        <v>229</v>
+      </c>
+      <c r="K25" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\桌面文件\sydwCx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D489E72-15B6-45C4-BB6F-78DE8D940547}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0B45CCB-0A9D-45CA-B229-8704A97E7E55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="275" uniqueCount="230">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="286" uniqueCount="240">
   <si>
     <t>s</t>
   </si>
@@ -933,6 +933,46 @@
   </si>
   <si>
     <t>自 2026年02月09日 至 2031年02月09日</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>北安市体育事业发展中心（北安市体育场馆服务中心）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>12231181777891949C</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>王兆华</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>68.93万元</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>北安市人民政府</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>财政补助（财政全额预算拨款）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>承担竞技体育项目训练和赛事工作，组织和指导体育宣传、科研和教育工作，负责优秀体育后备人才发展及全市体育人才队伍建设服务保障工作，指导和推进青少年体育工作，为主管部门开展体育运动反兴奋剂工作提供相关服务工作。承担市域内体育场馆的维护服务工作，为各类比赛、体育健身、项目训练等提供场地和器材。承担全民健身计划实施工作，负责公共体育设施的规划建设，指导群众体育组织建设。承担体育行业领域安全生产技术支撑和服务保障工作。开展国内外体育合作交流。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>北安市铁西区体育中心</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1FF433821BEB039EEC103E670B36E03E</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>自 2024年03月26日 至 2029年03月25日</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1327,7 +1367,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K25"/>
+  <dimension ref="A1:K26"/>
   <sheetFormatPr defaultColWidth="18.9296875" defaultRowHeight="21" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="18.9296875" style="1"/>
@@ -2218,6 +2258,41 @@
         <v>30</v>
       </c>
     </row>
+    <row r="26" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A26" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>230</v>
+      </c>
+      <c r="C26" s="5" t="s">
+        <v>231</v>
+      </c>
+      <c r="D26" s="5" t="s">
+        <v>236</v>
+      </c>
+      <c r="E26" s="5" t="s">
+        <v>237</v>
+      </c>
+      <c r="F26" s="5" t="s">
+        <v>232</v>
+      </c>
+      <c r="G26" s="5" t="s">
+        <v>235</v>
+      </c>
+      <c r="H26" s="5" t="s">
+        <v>233</v>
+      </c>
+      <c r="I26" s="5" t="s">
+        <v>234</v>
+      </c>
+      <c r="J26" s="4" t="s">
+        <v>239</v>
+      </c>
+      <c r="K26" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\桌面文件\sydwCx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0B45CCB-0A9D-45CA-B229-8704A97E7E55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7BEDB271-A371-4121-8678-649F4551A083}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -936,43 +936,43 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>北安市体育事业发展中心（北安市体育场馆服务中心）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>12231181777891949C</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>王兆华</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>68.93万元</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>北安市人民政府</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>财政补助（财政全额预算拨款）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>承担竞技体育项目训练和赛事工作，组织和指导体育宣传、科研和教育工作，负责优秀体育后备人才发展及全市体育人才队伍建设服务保障工作，指导和推进青少年体育工作，为主管部门开展体育运动反兴奋剂工作提供相关服务工作。承担市域内体育场馆的维护服务工作，为各类比赛、体育健身、项目训练等提供场地和器材。承担全民健身计划实施工作，负责公共体育设施的规划建设，指导群众体育组织建设。承担体育行业领域安全生产技术支撑和服务保障工作。开展国内外体育合作交流。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>北安市铁西区体育中心</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1FF433821BEB039EEC103E670B36E03E</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>自 2024年03月26日 至 2029年03月25日</t>
+    <t>浙江省体育彩票管理中心</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>12330000470053844F</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>5AC8BBF0D7DEAA448A5EA6E8C202EDFC</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>浙江省杭州市上城区复兴路397号复兴商务大厦南楼</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>为我省社会公益和体育事业发展提供服务。负责全省体育彩票公益品牌和责任彩票建设；组织实施全省体育彩票销售；负责全省体育彩票销售系统的建设、运维和维护，保障彩票销售安全；负责全省体育彩票销售渠道和场所规划、开奖兑奖；组织实施全省体育彩票的形象建设、彩票代销、营销宣传、人才队伍建设；授权和指导地方开展体育彩票销售管理等机构编制明确的内容</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>徐仁军</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>54106.61万元</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>浙江省体育局</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>财政适当补助（经费自理）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>自 2025年03月17日 至 2030年03月17日</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2216,7 +2216,7 @@
       <c r="I24" s="5" t="s">
         <v>219</v>
       </c>
-      <c r="J24" s="4" t="s">
+      <c r="J24" s="3" t="s">
         <v>220</v>
       </c>
       <c r="K24" s="1" t="s">
@@ -2251,7 +2251,7 @@
       <c r="I25" s="5" t="s">
         <v>225</v>
       </c>
-      <c r="J25" s="4" t="s">
+      <c r="J25" s="3" t="s">
         <v>229</v>
       </c>
       <c r="K25" s="1" t="s">
@@ -2260,7 +2260,7 @@
     </row>
     <row r="26" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A26" s="1" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="B26" s="5" t="s">
         <v>230</v>
@@ -2269,22 +2269,22 @@
         <v>231</v>
       </c>
       <c r="D26" s="5" t="s">
+        <v>234</v>
+      </c>
+      <c r="E26" s="5" t="s">
+        <v>233</v>
+      </c>
+      <c r="F26" s="5" t="s">
+        <v>235</v>
+      </c>
+      <c r="G26" s="5" t="s">
+        <v>238</v>
+      </c>
+      <c r="H26" s="5" t="s">
         <v>236</v>
       </c>
-      <c r="E26" s="5" t="s">
+      <c r="I26" s="5" t="s">
         <v>237</v>
-      </c>
-      <c r="F26" s="5" t="s">
-        <v>232</v>
-      </c>
-      <c r="G26" s="5" t="s">
-        <v>235</v>
-      </c>
-      <c r="H26" s="5" t="s">
-        <v>233</v>
-      </c>
-      <c r="I26" s="5" t="s">
-        <v>234</v>
       </c>
       <c r="J26" s="4" t="s">
         <v>239</v>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\桌面文件\sydwCx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7BEDB271-A371-4121-8678-649F4551A083}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1AB0685B-5238-48E6-9374-740ECB58CC70}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -944,10 +944,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>5AC8BBF0D7DEAA448A5EA6E8C202EDFC</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>浙江省杭州市上城区复兴路397号复兴商务大厦南楼</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -973,6 +969,10 @@
   </si>
   <si>
     <t>自 2025年03月17日 至 2030年03月17日</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>8D7A9A2D49F6DB758FE2396EA63A6D40</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2260,7 +2260,7 @@
     </row>
     <row r="26" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A26" s="1" t="s">
-        <v>232</v>
+        <v>239</v>
       </c>
       <c r="B26" s="5" t="s">
         <v>230</v>
@@ -2269,25 +2269,25 @@
         <v>231</v>
       </c>
       <c r="D26" s="5" t="s">
+        <v>233</v>
+      </c>
+      <c r="E26" s="5" t="s">
+        <v>232</v>
+      </c>
+      <c r="F26" s="5" t="s">
         <v>234</v>
       </c>
-      <c r="E26" s="5" t="s">
-        <v>233</v>
-      </c>
-      <c r="F26" s="5" t="s">
+      <c r="G26" s="5" t="s">
+        <v>237</v>
+      </c>
+      <c r="H26" s="5" t="s">
         <v>235</v>
       </c>
-      <c r="G26" s="5" t="s">
+      <c r="I26" s="5" t="s">
+        <v>236</v>
+      </c>
+      <c r="J26" s="4" t="s">
         <v>238</v>
-      </c>
-      <c r="H26" s="5" t="s">
-        <v>236</v>
-      </c>
-      <c r="I26" s="5" t="s">
-        <v>237</v>
-      </c>
-      <c r="J26" s="4" t="s">
-        <v>239</v>
       </c>
       <c r="K26" s="1" t="s">
         <v>30</v>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\桌面文件\sydwCx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1AB0685B-5238-48E6-9374-740ECB58CC70}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D40B6B23-5F7A-4D3E-8F26-84106A2008D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="286" uniqueCount="240">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="241">
   <si>
     <t>s</t>
   </si>
@@ -973,6 +973,10 @@
   </si>
   <si>
     <t>8D7A9A2D49F6DB758FE2396EA63A6D40</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>空</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1367,7 +1371,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K26"/>
+  <dimension ref="A1:K27"/>
   <sheetFormatPr defaultColWidth="18.9296875" defaultRowHeight="21" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="18.9296875" style="1"/>
@@ -2260,36 +2264,71 @@
     </row>
     <row r="26" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A26" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="F26" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="G26" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="H26" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="I26" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="J26" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="K26" s="1" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A27" s="1" t="s">
         <v>239</v>
       </c>
-      <c r="B26" s="5" t="s">
+      <c r="B27" s="5" t="s">
         <v>230</v>
       </c>
-      <c r="C26" s="5" t="s">
+      <c r="C27" s="5" t="s">
         <v>231</v>
       </c>
-      <c r="D26" s="5" t="s">
+      <c r="D27" s="5" t="s">
         <v>233</v>
       </c>
-      <c r="E26" s="5" t="s">
+      <c r="E27" s="5" t="s">
         <v>232</v>
       </c>
-      <c r="F26" s="5" t="s">
+      <c r="F27" s="5" t="s">
         <v>234</v>
       </c>
-      <c r="G26" s="5" t="s">
+      <c r="G27" s="5" t="s">
         <v>237</v>
       </c>
-      <c r="H26" s="5" t="s">
+      <c r="H27" s="5" t="s">
         <v>235</v>
       </c>
-      <c r="I26" s="5" t="s">
+      <c r="I27" s="5" t="s">
         <v>236</v>
       </c>
-      <c r="J26" s="4" t="s">
+      <c r="J27" s="4" t="s">
         <v>238</v>
       </c>
-      <c r="K26" s="1" t="s">
+      <c r="K27" s="1" t="s">
         <v>30</v>
       </c>
     </row>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\桌面文件\sydwCx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D40B6B23-5F7A-4D3E-8F26-84106A2008D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE1A9254-C92F-4C84-9D22-FD9062A23A53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="241">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="286" uniqueCount="239">
   <si>
     <t>s</t>
   </si>
@@ -936,47 +936,39 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>浙江省体育彩票管理中心</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>12330000470053844F</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>浙江省杭州市上城区复兴路397号复兴商务大厦南楼</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>为我省社会公益和体育事业发展提供服务。负责全省体育彩票公益品牌和责任彩票建设；组织实施全省体育彩票销售；负责全省体育彩票销售系统的建设、运维和维护，保障彩票销售安全；负责全省体育彩票销售渠道和场所规划、开奖兑奖；组织实施全省体育彩票的形象建设、彩票代销、营销宣传、人才队伍建设；授权和指导地方开展体育彩票销售管理等机构编制明确的内容</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>徐仁军</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>54106.61万元</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>浙江省体育局</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>财政适当补助（经费自理）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>自 2025年03月17日 至 2030年03月17日</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>8D7A9A2D49F6DB758FE2396EA63A6D40</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>空</t>
+    <t>潜江市高石碑镇小学</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>12429005421560823F</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>许立荣</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>5425857F83F06DE92ECC7FFA518F50AC</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>实施小学义务教育，促进基础教育发展。 小学学历教育</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>潜江市高石碑镇钟长路60号</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>289万元</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>潜江市教育局</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>自 2026年02月06日 至 2031年02月05日</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1371,7 +1363,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K27"/>
+  <dimension ref="A1:K26"/>
   <sheetFormatPr defaultColWidth="18.9296875" defaultRowHeight="21" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="18.9296875" style="1"/>
@@ -2264,71 +2256,36 @@
     </row>
     <row r="26" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A26" s="1" t="s">
-        <v>240</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>240</v>
-      </c>
-      <c r="C26" s="1" t="s">
-        <v>240</v>
-      </c>
-      <c r="D26" s="1" t="s">
-        <v>240</v>
-      </c>
-      <c r="E26" s="1" t="s">
-        <v>240</v>
-      </c>
-      <c r="F26" s="1" t="s">
-        <v>240</v>
-      </c>
-      <c r="G26" s="1" t="s">
-        <v>240</v>
-      </c>
-      <c r="H26" s="1" t="s">
-        <v>240</v>
-      </c>
-      <c r="I26" s="1" t="s">
-        <v>240</v>
-      </c>
-      <c r="J26" s="1" t="s">
-        <v>240</v>
+        <v>233</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>230</v>
+      </c>
+      <c r="C26" s="5" t="s">
+        <v>231</v>
+      </c>
+      <c r="D26" s="5" t="s">
+        <v>234</v>
+      </c>
+      <c r="E26" s="5" t="s">
+        <v>235</v>
+      </c>
+      <c r="F26" s="5" t="s">
+        <v>232</v>
+      </c>
+      <c r="G26" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="H26" s="5" t="s">
+        <v>236</v>
+      </c>
+      <c r="I26" s="5" t="s">
+        <v>237</v>
+      </c>
+      <c r="J26" s="4" t="s">
+        <v>238</v>
       </c>
       <c r="K26" s="1" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="27" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A27" s="1" t="s">
-        <v>239</v>
-      </c>
-      <c r="B27" s="5" t="s">
-        <v>230</v>
-      </c>
-      <c r="C27" s="5" t="s">
-        <v>231</v>
-      </c>
-      <c r="D27" s="5" t="s">
-        <v>233</v>
-      </c>
-      <c r="E27" s="5" t="s">
-        <v>232</v>
-      </c>
-      <c r="F27" s="5" t="s">
-        <v>234</v>
-      </c>
-      <c r="G27" s="5" t="s">
-        <v>237</v>
-      </c>
-      <c r="H27" s="5" t="s">
-        <v>235</v>
-      </c>
-      <c r="I27" s="5" t="s">
-        <v>236</v>
-      </c>
-      <c r="J27" s="4" t="s">
-        <v>238</v>
-      </c>
-      <c r="K27" s="1" t="s">
         <v>30</v>
       </c>
     </row>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\桌面文件\sydwCx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE1A9254-C92F-4C84-9D22-FD9062A23A53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56074782-8CD2-41B3-9619-DF18AD4A183A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="286" uniqueCount="239">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="248">
   <si>
     <t>s</t>
   </si>
@@ -969,6 +969,42 @@
   </si>
   <si>
     <t>自 2026年02月06日 至 2031年02月05日</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>合肥师范学院</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>12340000485002433U</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>28DE85F5A64CEACB7E4D01AB53CD2C5A</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>18698万元</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>安徽省教育厅</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>自 2022年04月21日 至 2027年04月21日</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>合肥市金寨路327号</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>是一所省属全日制普通本科院校。以本科教育为主，开展硕士研究生教育，培养新型师资和应用型人才；开展科学研究、科技开发与服务等；同时承担全省中小学教师学历补偿教育，提高教育以及全省完中、职中校长和教育行政干部培训任务等。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>方东玲</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1363,7 +1399,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K26"/>
+  <dimension ref="A1:K27"/>
   <sheetFormatPr defaultColWidth="18.9296875" defaultRowHeight="21" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="18.9296875" style="1"/>
@@ -2289,6 +2325,41 @@
         <v>30</v>
       </c>
     </row>
+    <row r="27" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A27" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>239</v>
+      </c>
+      <c r="C27" s="5" t="s">
+        <v>240</v>
+      </c>
+      <c r="D27" s="5" t="s">
+        <v>246</v>
+      </c>
+      <c r="E27" s="5" t="s">
+        <v>245</v>
+      </c>
+      <c r="F27" s="5" t="s">
+        <v>247</v>
+      </c>
+      <c r="G27" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="H27" s="5" t="s">
+        <v>242</v>
+      </c>
+      <c r="I27" s="5" t="s">
+        <v>243</v>
+      </c>
+      <c r="J27" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="K27" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\桌面文件\sydwCx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56074782-8CD2-41B3-9619-DF18AD4A183A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1F5BE7C-F26E-4BA6-BCB9-4F75AD9A508B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="248">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="308" uniqueCount="256">
   <si>
     <t>s</t>
   </si>
@@ -1005,6 +1005,38 @@
   </si>
   <si>
     <t>方东玲</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>绍兴大学</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>12330600471322006J</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>高等教育教学、成人教育教学、医疗服务，所属企业经营服务，科学研究和社会服务（涉及资质许可项目需持有资质证书开展）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>绍兴市城南大道1077号</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>赵阳</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>516196.27万元</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>自 2026年02月14日 至 2027年03月30日</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>90882FA9FE2137D8905F5FBDAB68DB82</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1399,7 +1431,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K27"/>
+  <dimension ref="A1:K28"/>
   <sheetFormatPr defaultColWidth="18.9296875" defaultRowHeight="21" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="18.9296875" style="1"/>
@@ -2360,6 +2392,41 @@
         <v>30</v>
       </c>
     </row>
+    <row r="28" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A28" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="B28" s="5" t="s">
+        <v>248</v>
+      </c>
+      <c r="C28" s="5" t="s">
+        <v>249</v>
+      </c>
+      <c r="D28" s="5" t="s">
+        <v>250</v>
+      </c>
+      <c r="E28" s="5" t="s">
+        <v>251</v>
+      </c>
+      <c r="F28" s="5" t="s">
+        <v>252</v>
+      </c>
+      <c r="G28" s="5" t="s">
+        <v>172</v>
+      </c>
+      <c r="H28" s="5" t="s">
+        <v>253</v>
+      </c>
+      <c r="I28" s="5" t="s">
+        <v>248</v>
+      </c>
+      <c r="J28" s="4" t="s">
+        <v>254</v>
+      </c>
+      <c r="K28" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\桌面文件\sydwCx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1F5BE7C-F26E-4BA6-BCB9-4F75AD9A508B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{967FEDFB-7E87-4F75-A70C-527360D914D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="308" uniqueCount="256">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="319" uniqueCount="265">
   <si>
     <t>s</t>
   </si>
@@ -1037,6 +1037,42 @@
   </si>
   <si>
     <t>90882FA9FE2137D8905F5FBDAB68DB82</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>西南科技大学</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>125100007175954436</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>四川省绵阳市涪城区</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>培养普通教育和成人教育大学专科、本科、研究生等各层次高等专业技术人才，开展科学研究、科技开发服务等</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>祝效华</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>23820万元</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>四川省教育厅</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>自 2023年07月06日 至 2028年07月05日</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2451BB5231C81953EFA96AC96ED098AA</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1431,7 +1467,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K28"/>
+  <dimension ref="A1:K29"/>
   <sheetFormatPr defaultColWidth="18.9296875" defaultRowHeight="21" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="18.9296875" style="1"/>
@@ -2427,6 +2463,41 @@
         <v>30</v>
       </c>
     </row>
+    <row r="29" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A29" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="B29" s="5" t="s">
+        <v>256</v>
+      </c>
+      <c r="C29" s="5" t="s">
+        <v>257</v>
+      </c>
+      <c r="D29" s="5" t="s">
+        <v>259</v>
+      </c>
+      <c r="E29" s="5" t="s">
+        <v>258</v>
+      </c>
+      <c r="F29" s="5" t="s">
+        <v>260</v>
+      </c>
+      <c r="G29" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="H29" s="5" t="s">
+        <v>261</v>
+      </c>
+      <c r="I29" s="5" t="s">
+        <v>262</v>
+      </c>
+      <c r="J29" s="4" t="s">
+        <v>263</v>
+      </c>
+      <c r="K29" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\桌面文件\sydwCx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{967FEDFB-7E87-4F75-A70C-527360D914D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29B53BB4-A17B-4520-B460-656589F826BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="319" uniqueCount="265">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="330" uniqueCount="275">
   <si>
     <t>s</t>
   </si>
@@ -1073,6 +1073,46 @@
   </si>
   <si>
     <t>2451BB5231C81953EFA96AC96ED098AA</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>常宁市板桥镇新塘幼儿园</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>12430482MB1N93078W</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>常宁市板桥镇西洞村</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>为学龄前儿童提供保育和教育服务 幼儿保育、幼儿教育</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>刘满英</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>非财政补助</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>23万元</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>常宁市教育局</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>自 2025年03月19日 至 2027年03月18日</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>F112B6DB7148FCE914CC89B3D9F2B673</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1467,7 +1507,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K29"/>
+  <dimension ref="A1:K30"/>
   <sheetFormatPr defaultColWidth="18.9296875" defaultRowHeight="21" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="18.9296875" style="1"/>
@@ -2498,6 +2538,41 @@
         <v>30</v>
       </c>
     </row>
+    <row r="30" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A30" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="B30" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="C30" s="5" t="s">
+        <v>266</v>
+      </c>
+      <c r="D30" s="5" t="s">
+        <v>268</v>
+      </c>
+      <c r="E30" s="5" t="s">
+        <v>267</v>
+      </c>
+      <c r="F30" s="5" t="s">
+        <v>269</v>
+      </c>
+      <c r="G30" s="5" t="s">
+        <v>270</v>
+      </c>
+      <c r="H30" s="5" t="s">
+        <v>271</v>
+      </c>
+      <c r="I30" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="J30" s="4" t="s">
+        <v>273</v>
+      </c>
+      <c r="K30" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\桌面文件\sydwCx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29B53BB4-A17B-4520-B460-656589F826BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D4CE830-E469-435C-9992-231BD3DDB0B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="330" uniqueCount="275">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="352" uniqueCount="294">
   <si>
     <t>s</t>
   </si>
@@ -1113,6 +1113,82 @@
   </si>
   <si>
     <t>F112B6DB7148FCE914CC89B3D9F2B673</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>西北信息报社</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>12610000435231481D</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>225E28BCB2AABB3F8B508E0485387E05</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>王瑞华</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>193万元</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>陕西省工业和信息化厅信息中心</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>西安市新城省政府大楼7楼15号</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>报道经济信息，促进经济发展。报纸出版发行、广告发布。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>自 2023年03月01日 至 2028年03月01日</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>山东省青岛体育训练中心</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>12370000F676183819</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>C146DA6C8ADB05CF9274BF3E9F2D6D3B</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>谢长清</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>13485万元</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>财政拨款</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>山东省体育局</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>青岛市市北区延安一路31号</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>承担全省射箭、击剑、现代五项、帆船、帆板、航海模型、马术、冬季运动项目的管理和相关优秀运动队的训练、参赛工作。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>自 2025年07月29日 至 2026年03月21日</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1507,7 +1583,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K30"/>
+  <dimension ref="A1:K32"/>
   <sheetFormatPr defaultColWidth="18.9296875" defaultRowHeight="21" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="18.9296875" style="1"/>
@@ -2573,6 +2649,76 @@
         <v>30</v>
       </c>
     </row>
+    <row r="31" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A31" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="B31" s="5" t="s">
+        <v>275</v>
+      </c>
+      <c r="C31" s="5" t="s">
+        <v>276</v>
+      </c>
+      <c r="D31" s="5" t="s">
+        <v>282</v>
+      </c>
+      <c r="E31" s="5" t="s">
+        <v>281</v>
+      </c>
+      <c r="F31" s="5" t="s">
+        <v>278</v>
+      </c>
+      <c r="G31" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="H31" s="5" t="s">
+        <v>279</v>
+      </c>
+      <c r="I31" s="5" t="s">
+        <v>280</v>
+      </c>
+      <c r="J31" s="4" t="s">
+        <v>283</v>
+      </c>
+      <c r="K31" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A32" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="B32" s="5" t="s">
+        <v>284</v>
+      </c>
+      <c r="C32" s="5" t="s">
+        <v>285</v>
+      </c>
+      <c r="D32" s="5" t="s">
+        <v>292</v>
+      </c>
+      <c r="E32" s="5" t="s">
+        <v>291</v>
+      </c>
+      <c r="F32" s="5" t="s">
+        <v>287</v>
+      </c>
+      <c r="G32" s="5" t="s">
+        <v>289</v>
+      </c>
+      <c r="H32" s="5" t="s">
+        <v>288</v>
+      </c>
+      <c r="I32" s="5" t="s">
+        <v>290</v>
+      </c>
+      <c r="J32" s="4" t="s">
+        <v>293</v>
+      </c>
+      <c r="K32" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\桌面文件\sydwCx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D4CE830-E469-435C-9992-231BD3DDB0B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7676C646-CFAA-438C-B4FC-9186778B1C79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="352" uniqueCount="294">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="363" uniqueCount="304">
   <si>
     <t>s</t>
   </si>
@@ -1189,6 +1189,46 @@
   </si>
   <si>
     <t>自 2025年07月29日 至 2026年03月21日</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>成都市青羊区中医医院</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1251010545077664X7</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>6A99F7C4D166F71C7961CE2DD06CB891</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>42879万元</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>财政补助（差额补贴）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>成都市青羊区卫生健康局</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>成都市光华村街11号</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>中医、内、外、妇、儿、眼、耳鼻喉、口腔、麻醉、康复、医学检验、医学影像，养老服务、培训等业务。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>李进</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>自 2025年7月01日 至 2030年06月30日</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1583,7 +1623,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K32"/>
+  <dimension ref="A1:K33"/>
   <sheetFormatPr defaultColWidth="18.9296875" defaultRowHeight="21" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="18.9296875" style="1"/>
@@ -2719,6 +2759,41 @@
         <v>30</v>
       </c>
     </row>
+    <row r="33" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A33" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="B33" s="5" t="s">
+        <v>294</v>
+      </c>
+      <c r="C33" s="5" t="s">
+        <v>295</v>
+      </c>
+      <c r="D33" s="5" t="s">
+        <v>301</v>
+      </c>
+      <c r="E33" s="5" t="s">
+        <v>300</v>
+      </c>
+      <c r="F33" s="5" t="s">
+        <v>302</v>
+      </c>
+      <c r="G33" s="5" t="s">
+        <v>298</v>
+      </c>
+      <c r="H33" s="5" t="s">
+        <v>297</v>
+      </c>
+      <c r="I33" s="5" t="s">
+        <v>299</v>
+      </c>
+      <c r="J33" s="4" t="s">
+        <v>303</v>
+      </c>
+      <c r="K33" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\桌面文件\sydwCx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7676C646-CFAA-438C-B4FC-9186778B1C79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AAA0E62B-CB82-4881-9E6A-002F617B5347}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\桌面文件\sydwCx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AAA0E62B-CB82-4881-9E6A-002F617B5347}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50216D21-D353-4D8F-85C9-BAA5F66CBA7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="363" uniqueCount="304">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="374" uniqueCount="314">
   <si>
     <t>s</t>
   </si>
@@ -1228,7 +1228,47 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>自 2025年7月01日 至 2030年06月30日</t>
+    <t>中山大学孙逸仙纪念医院</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>12100000455416037C</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>为人民身体健康提供医疗与护理保健服务。 预防保健、内、外、妇产、儿、眼、耳鼻咽喉、口腔、皮肤、急诊医学、康复医学、麻醉、医学检验、病理、医学影像、中医科诊疗与护理 医学教学与医学研究 卫生医疗人员培训 卫生技术人员培训 保健与健康教育</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>广东省广州市沿江西路107号</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>陈样新</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>非财政补助 （事业收入）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>45000万元</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>中山大学</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>自 2026年01月15日 至 2031年01月14日</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>自 2025年07月01日 至 2030年06月30日</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>A5358944E541450B08F65E4B276241D2</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1623,7 +1663,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K33"/>
+  <dimension ref="A1:K34"/>
   <sheetFormatPr defaultColWidth="18.9296875" defaultRowHeight="21" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="18.9296875" style="1"/>
@@ -2788,9 +2828,44 @@
         <v>299</v>
       </c>
       <c r="J33" s="4" t="s">
+        <v>312</v>
+      </c>
+      <c r="K33" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A34" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="B34" s="5" t="s">
         <v>303</v>
       </c>
-      <c r="K33" s="1" t="s">
+      <c r="C34" s="5" t="s">
+        <v>304</v>
+      </c>
+      <c r="D34" s="5" t="s">
+        <v>305</v>
+      </c>
+      <c r="E34" s="5" t="s">
+        <v>306</v>
+      </c>
+      <c r="F34" s="5" t="s">
+        <v>307</v>
+      </c>
+      <c r="G34" s="5" t="s">
+        <v>308</v>
+      </c>
+      <c r="H34" s="5" t="s">
+        <v>309</v>
+      </c>
+      <c r="I34" s="5" t="s">
+        <v>310</v>
+      </c>
+      <c r="J34" s="3" t="s">
+        <v>311</v>
+      </c>
+      <c r="K34" s="1" t="s">
         <v>30</v>
       </c>
     </row>
